--- a/data/trans_dic/P21D_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,17</t>
+          <t>0,0; 0,16</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1036</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1392</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2517</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1393</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1768</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1596</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1247</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1370</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2054</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1816</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1243</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1002</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1354</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1201</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4897</t>
+          <t>0; 5798</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4260</t>
+          <t>0; 4766</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 1294</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>0; 4426</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 5380</t>
+          <t>0; 5358</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Provincia-trans_dic.xlsx
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5798</t>
+          <t>0; 4507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4766</t>
+          <t>0; 5033</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 4426</t>
+          <t>0; 5349</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 5358</t>
+          <t>0; 5120</t>
         </is>
       </c>
     </row>
